--- a/SkillDatatable.xlsx
+++ b/SkillDatatable.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\SBSAcademy_Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC1605-33F0-47F1-BDFF-274F166249FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9938249A-30FB-46F0-AB16-D7E89205CBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
   <sheets>
     <sheet name="LightSKilltable" sheetId="1" r:id="rId1"/>
     <sheet name="HeavySkilltable" sheetId="8" r:id="rId2"/>
     <sheet name="UtilitySkilltable" sheetId="9" r:id="rId3"/>
-    <sheet name="Fusiontable" sheetId="12" r:id="rId4"/>
-    <sheet name="Raritytable" sheetId="10" r:id="rId5"/>
-    <sheet name="Elementtable" sheetId="13" r:id="rId6"/>
+    <sheet name="FusionSkilltable" sheetId="12" r:id="rId4"/>
+    <sheet name="Skill_Rarity" sheetId="10" r:id="rId5"/>
+    <sheet name="Element_id" sheetId="13" r:id="rId6"/>
     <sheet name="AreaType" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -51,7 +51,7 @@
     <author>tc={074FA935-8F2B-432E-A31A-643FCF6FAFED}</author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -59,7 +59,7 @@
     상성 시스템 추가 시 필요</t>
       </text>
     </comment>
-    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
+    <comment ref="I2" authorId="1" shapeId="0" xr:uid="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="234">
   <si>
     <t>num</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -109,10 +109,6 @@
   </si>
   <si>
     <t>Skill_name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_name_key</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -982,6 +978,18 @@
   </si>
   <si>
     <t>SKILL_RAPID_RECOVERY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity_Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어도 가중치</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -989,7 +997,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,12 +1020,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1157,13 +1159,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1508,10 +1510,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G2" dT="2026-10-21T17:17:46.30" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
+  <threadedComment ref="H2" dT="2026-10-21T17:17:46.30" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
     <text>상성 시스템 추가 시 필요</text>
   </threadedComment>
-  <threadedComment ref="H2" dT="2026-10-21T17:17:55.72" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
+  <threadedComment ref="I2" dT="2026-10-21T17:17:55.72" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
     <text>상성 시스템 추가 시 필요</text>
   </threadedComment>
 </ThreadedComments>
@@ -1520,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A07B8D-296F-4731-B27A-9CC1CD5CA71B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
@@ -1529,81 +1531,80 @@
     <col min="5" max="5" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -1636,35 +1637,29 @@
       <c r="AA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>46</v>
+      <c r="AD1" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1678,27 +1673,27 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M2" s="3" t="s">
@@ -1707,7 +1702,7 @@
       <c r="N2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -1743,7 +1738,7 @@
       <c r="Z2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="AB2" s="3" t="s">
@@ -1753,28 +1748,22 @@
         <v>23</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AE2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A13">IF(C3:INDEX(C:C, 2+COUNT(C3:C1000))&lt;&gt;"", "LskillData", "")</f>
         <v>LskillData</v>
@@ -1788,26 +1777,26 @@
         <v>10001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1818,25 +1807,25 @@
         <v>10002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1847,25 +1836,25 @@
         <v>10003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1876,25 +1865,25 @@
         <v>10004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1905,25 +1894,25 @@
         <v>10005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1934,25 +1923,25 @@
         <v>10006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1963,25 +1952,25 @@
         <v>10007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -1992,25 +1981,25 @@
         <v>10008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -2021,25 +2010,25 @@
         <v>10009</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>98</v>
+      <c r="I11" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -2050,25 +2039,25 @@
         <v>10010</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>100</v>
+      <c r="I12" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v>LskillData</v>
       </c>
@@ -2078,24 +2067,32 @@
       <c r="C13" s="1">
         <v>10011</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>107</v>
+      <c r="I13" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2105,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A61791-D6B5-4A42-9C5C-B3B9F96B250E}">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
@@ -2116,80 +2113,79 @@
     <col min="6" max="6" width="22.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9" style="1"/>
+    <col min="9" max="10" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="K1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -2222,35 +2218,29 @@
       <c r="AA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>46</v>
+      <c r="AD1" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2264,27 +2254,27 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M2" s="3" t="s">
@@ -2293,7 +2283,7 @@
       <c r="N2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -2329,7 +2319,7 @@
       <c r="Z2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="AB2" s="3" t="s">
@@ -2339,28 +2329,22 @@
         <v>23</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AE2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A7">IF(C3:INDEX(C:C, 2+COUNT(C3:C1000))&lt;&gt;"", "HskillData", "")</f>
         <v>HskillData</v>
@@ -2370,27 +2354,27 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" cm="1">
-        <f t="array" ref="C3:C7">IF(COUNTA(D3:D1000)=0, "", _xlfn.SEQUENCE(COUNTA(D3:D1000), 1, 10001, 1))</f>
-        <v>10001</v>
+        <f t="array" ref="C3:C7">IF(COUNTA(D3:D1000)=0, "", _xlfn.SEQUENCE(COUNTA(D3:D1000), 1, 20001, 1))</f>
+        <v>20001</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>HskillData</v>
       </c>
@@ -2398,25 +2382,25 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>10002</v>
+        <v>20002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>HskillData</v>
       </c>
@@ -2424,25 +2408,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>10003</v>
+        <v>20003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>HskillData</v>
       </c>
@@ -2450,25 +2434,25 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>10004</v>
+        <v>20004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>HskillData</v>
       </c>
@@ -2476,25 +2460,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>10005</v>
+        <v>20005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="E13" s="7"/>
     </row>
   </sheetData>
@@ -2505,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{686351B3-D75F-4D77-AF49-9090715D2EEA}">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
@@ -2515,81 +2499,80 @@
     <col min="6" max="6" width="26.5" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="K1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -2622,35 +2605,29 @@
       <c r="AA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>46</v>
+      <c r="AD1" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2664,27 +2641,27 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M2" s="3" t="s">
@@ -2693,7 +2670,7 @@
       <c r="N2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -2729,7 +2706,7 @@
       <c r="Z2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="AB2" s="3" t="s">
@@ -2739,28 +2716,22 @@
         <v>23</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AE2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A12">IF(C3:INDEX(C:C, 2+COUNT(C3:C1000))&lt;&gt;"", "UskillData", "")</f>
         <v>UskillData</v>
@@ -2770,24 +2741,24 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" cm="1">
-        <f t="array" ref="C3:C12">IF(COUNTA(D3:D1000)=0, "", _xlfn.SEQUENCE(COUNTA(D3:D1000), 1, 10001, 1))</f>
-        <v>10001</v>
+        <f t="array" ref="C3:C12">IF(COUNTA(D3:D1000)=0, "", _xlfn.SEQUENCE(COUNTA(D3:D1000), 1, 30001, 1))</f>
+        <v>30001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2795,22 +2766,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>10002</v>
+        <v>30002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2818,22 +2789,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>10003</v>
+        <v>30003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2841,22 +2812,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>10004</v>
+        <v>30004</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2864,22 +2835,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>10005</v>
+        <v>30005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I7" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2887,22 +2858,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>10006</v>
+        <v>30006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2910,22 +2881,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>10007</v>
+        <v>30007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2933,22 +2904,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>10008</v>
+        <v>30008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I10" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2956,22 +2927,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="1">
-        <v>10009</v>
+        <v>30009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v>UskillData</v>
       </c>
@@ -2979,19 +2950,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="1">
-        <v>10010</v>
+        <v>30010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3002,7 +2973,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4585EC-28B6-4EF6-972E-BC0BB398BE58}">
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
@@ -3043,27 +3014,26 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-      <c r="L1" s="13"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="AA1" s="5"/>
@@ -3078,23 +3048,23 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
@@ -3142,93 +3112,6 @@
         <f>IF(G3="","", IFERROR(VLOOKUP(G3, LightSKilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, HeavySkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, UtilitySkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))))</f>
         <v>플레어 탄환</v>
       </c>
-      <c r="L3" s="13"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="L5" s="13"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="E10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="L11" s="13"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="H12" s="13"/>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="H13" s="13"/>
-      <c r="L13" s="13"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="H14" s="13"/>
-      <c r="L14" s="13"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="H15" s="13"/>
-      <c r="L15" s="13"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="H16" s="13"/>
-      <c r="L16" s="13"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H17" s="13"/>
-      <c r="L17" s="13"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H18" s="13"/>
-      <c r="L18" s="13"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3241,25 +3124,36 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11F613E-218D-4C8F-A69F-11181025131C}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3267,13 +3161,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A100">IF(C3:C100="","", "RarityData")</f>
         <v>RarityData</v>
@@ -3283,13 +3186,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="E3" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3297,13 +3203,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="E4" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3311,13 +3220,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3325,13 +3237,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3339,13 +3254,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3353,13 +3271,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3367,43 +3288,46 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v/>
       </c>
@@ -3831,12 +3755,13 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51ACD7B-A0C5-4F99-B733-4FAD1F959008}">
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AG100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
@@ -3845,69 +3770,72 @@
     <col min="4" max="4" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="25.875" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.875" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="5"/>
+      <c r="J1" s="7"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="13"/>
-      <c r="O1" s="5"/>
+      <c r="M1" s="5"/>
       <c r="P1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AD1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="AC1" s="5"/>
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
-    </row>
-    <row r="2" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AG1" s="5"/>
+    </row>
+    <row r="2" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3915,25 +3843,27 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>161</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="O2" s="11"/>
+      <c r="J2" s="6"/>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
@@ -3945,8 +3875,9 @@
       <c r="X2" s="11"/>
       <c r="Y2" s="11"/>
       <c r="Z2" s="11"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AA2" s="11"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A100">IF(C3:C100="","", "ElmentData")</f>
         <v>ElmentData</v>
@@ -3956,19 +3887,18 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="F3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -3976,19 +3906,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -3996,19 +3923,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="M5" s="13"/>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4016,19 +3940,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="M6" s="13"/>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4036,19 +3957,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="M7" s="13"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4056,19 +3974,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="M8" s="13"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4076,19 +3991,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="M9" s="13"/>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4096,39 +4008,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="str">
+        <v>ElmentData</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="M10" s="13"/>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="str">
-        <v>ElmentData</v>
-      </c>
-      <c r="B11" s="13">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="M11" s="13"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v>ElmentData</v>
       </c>
@@ -4136,137 +4042,111 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="M12" s="13"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v/>
       </c>
-      <c r="I13" s="13"/>
-      <c r="M13" s="13"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v/>
       </c>
-      <c r="I14" s="13"/>
-      <c r="M14" s="13"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v/>
       </c>
-      <c r="I15" s="13"/>
-      <c r="M15" s="13"/>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v/>
       </c>
-      <c r="I16" s="13"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <v/>
       </c>
-      <c r="I17" s="13"/>
-      <c r="M17" s="13"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
         <v/>
       </c>
-      <c r="I18" s="13"/>
-      <c r="M18" s="13"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
         <v/>
       </c>
@@ -4631,10 +4511,10 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4645,10 +4525,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/SkillDatatable.xlsx
+++ b/SkillDatatable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9938249A-30FB-46F0-AB16-D7E89205CBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4708A388-F3BE-4A9E-AF20-97B3A9A1ED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
@@ -510,10 +510,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SKill_explanation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Material_SkillA_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -990,6 +986,10 @@
   </si>
   <si>
     <t>레어도 가중치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_explanation</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1569,7 +1569,7 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
@@ -1581,7 +1581,7 @@
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>68</v>
@@ -1673,10 +1673,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>62</v>
@@ -1685,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>27</v>
@@ -1760,7 +1760,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -1780,16 +1780,16 @@
         <v>57</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>69</v>
@@ -1810,16 +1810,16 @@
         <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>69</v>
@@ -1839,16 +1839,16 @@
         <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>69</v>
@@ -1868,16 +1868,16 @@
         <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>88</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>69</v>
@@ -1897,16 +1897,16 @@
         <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>88</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>69</v>
@@ -1926,16 +1926,16 @@
         <v>91</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>90</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>69</v>
@@ -1955,16 +1955,16 @@
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>69</v>
@@ -1984,16 +1984,16 @@
         <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>69</v>
@@ -2013,16 +2013,16 @@
         <v>96</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>97</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>69</v>
@@ -2042,16 +2042,16 @@
         <v>98</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>99</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>69</v>
@@ -2068,19 +2068,19 @@
         <v>10011</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>69</v>
@@ -2102,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A61791-D6B5-4A42-9C5C-B3B9F96B250E}">
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
@@ -2150,7 +2150,7 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
@@ -2162,7 +2162,7 @@
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>26</v>
@@ -2254,10 +2254,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>62</v>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>27</v>
@@ -2341,7 +2341,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2358,19 +2358,19 @@
         <v>20001</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2385,19 +2385,19 @@
         <v>20002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2411,19 +2411,19 @@
         <v>20003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2437,19 +2437,19 @@
         <v>20004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2463,23 +2463,20 @@
         <v>20005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="E13" s="7"/>
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2537,7 +2534,7 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
@@ -2549,7 +2546,7 @@
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>26</v>
@@ -2641,10 +2638,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>62</v>
@@ -2653,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>27</v>
@@ -2728,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2745,16 +2742,16 @@
         <v>30001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2769,16 +2766,16 @@
         <v>30002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2792,16 +2789,16 @@
         <v>30003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2815,16 +2812,16 @@
         <v>30004</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2838,16 +2835,16 @@
         <v>30005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -2861,16 +2858,16 @@
         <v>30006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -2884,16 +2881,16 @@
         <v>30007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -2907,16 +2904,16 @@
         <v>30008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2930,16 +2927,16 @@
         <v>30009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2953,16 +2950,16 @@
         <v>30010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2976,13 +2973,13 @@
   <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -3020,16 +3017,16 @@
         <v>51</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -3055,16 +3052,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
@@ -3127,11 +3124,11 @@
   <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
@@ -3144,7 +3141,7 @@
         <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>65</v>
@@ -3167,7 +3164,7 @@
         <v>72</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>64</v>
@@ -3288,7 +3285,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>86</v>
@@ -3771,8 +3768,8 @@
     <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.125" style="1" bestFit="1" customWidth="1"/>
@@ -3807,22 +3804,22 @@
         <v>24</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="J1" s="7"/>
       <c r="K1" s="5"/>
@@ -3843,25 +3840,25 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="J2" s="6"/>
       <c r="P2" s="11"/>
@@ -3887,13 +3884,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F3" s="8"/>
       <c r="J3" s="8"/>
@@ -3906,13 +3903,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -3923,13 +3920,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -3940,13 +3937,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -3957,13 +3954,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -3974,13 +3971,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -3991,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -4008,13 +4005,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -4025,13 +4022,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -4042,13 +4039,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -4503,7 +4500,9 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/SkillDatatable.xlsx
+++ b/SkillDatatable.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1119,7 +1119,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1163,9 +1163,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1522,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A07B8D-296F-4731-B27A-9CC1CD5CA71B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
@@ -2067,10 +2064,10 @@
       <c r="C13" s="1">
         <v>10011</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="1" t="s">
         <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -2085,14 +2082,6 @@
       <c r="J13" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SkillDatatable.xlsx
+++ b/SkillDatatable.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4708A388-F3BE-4A9E-AF20-97B3A9A1ED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A48EF2-21A9-4457-B47C-A2E0C668B4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
   <sheets>
-    <sheet name="LightSKilltable" sheetId="1" r:id="rId1"/>
+    <sheet name="LightSkilltable" sheetId="1" r:id="rId1"/>
     <sheet name="HeavySkilltable" sheetId="8" r:id="rId2"/>
     <sheet name="UtilitySkilltable" sheetId="9" r:id="rId3"/>
     <sheet name="FusionSkilltable" sheetId="12" r:id="rId4"/>
@@ -373,15 +373,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>소모 자원 종류
-(HP/MP)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>레어도</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -990,6 +981,15 @@
   </si>
   <si>
     <t>Skill_explanation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모 자원 종류
+(HP/ST)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1042,7 +1042,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1107,6 +1107,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1119,7 +1132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1163,6 +1176,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1566,22 +1585,22 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>68</v>
+        <v>203</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>233</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>28</v>
@@ -1653,7 +1672,7 @@
         <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1666,25 +1685,25 @@
       <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>27</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1757,7 +1776,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -1776,20 +1795,21 @@
       <c r="D3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>69</v>
+      <c r="E3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -1807,19 +1827,19 @@
         <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -1836,19 +1856,19 @@
         <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -1865,19 +1885,19 @@
         <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -1894,19 +1914,19 @@
         <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -1920,22 +1940,22 @@
         <v>10006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -1949,22 +1969,22 @@
         <v>10007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -1978,22 +1998,22 @@
         <v>10008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2007,22 +2027,22 @@
         <v>10009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2036,22 +2056,22 @@
         <v>10010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -2065,22 +2085,22 @@
         <v>10011</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2139,7 +2159,7 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
@@ -2151,7 +2171,7 @@
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>26</v>
@@ -2226,7 +2246,7 @@
         <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2243,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>62</v>
@@ -2255,7 +2275,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>27</v>
@@ -2330,7 +2350,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2347,19 +2367,19 @@
         <v>20001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2374,19 +2394,19 @@
         <v>20002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2400,19 +2420,19 @@
         <v>20003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2426,19 +2446,19 @@
         <v>20004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2452,19 +2472,19 @@
         <v>20005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2543,7 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>52</v>
@@ -2535,7 +2555,7 @@
         <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>26</v>
@@ -2610,7 +2630,7 @@
         <v>56</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2627,10 +2647,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>62</v>
@@ -2639,7 +2659,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>27</v>
@@ -2714,7 +2734,7 @@
         <v>55</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2731,16 +2751,16 @@
         <v>30001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2755,16 +2775,16 @@
         <v>30002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2778,16 +2798,16 @@
         <v>30003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2801,16 +2821,16 @@
         <v>30004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2824,16 +2844,16 @@
         <v>30005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -2847,16 +2867,16 @@
         <v>30006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -2870,16 +2890,16 @@
         <v>30007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -2893,16 +2913,16 @@
         <v>30008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2916,16 +2936,16 @@
         <v>30009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2939,16 +2959,16 @@
         <v>30010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3006,16 +3026,16 @@
         <v>51</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -3041,16 +3061,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
@@ -3075,27 +3095,27 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <f>LightSKilltable!C13</f>
+        <f>LightSkilltable!C13</f>
         <v>10011</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f>IF(C3="","", IFERROR(VLOOKUP(C3, LightSKilltable!$C$3:$D$1000, 2, FALSE), "미등록"))</f>
+        <f>IF(C3="","", IFERROR(VLOOKUP(C3, LightSkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))</f>
         <v>태양 검</v>
       </c>
       <c r="E3" s="8">
-        <f>LightSKilltable!C9</f>
+        <f>LightSkilltable!C9</f>
         <v>10007</v>
       </c>
       <c r="F3" s="1" t="str">
-        <f>IF(E3="","", IFERROR(VLOOKUP(E3, LightSKilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(E3, HeavySkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(E3, UtilitySkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))))</f>
+        <f>IF(E3="","", IFERROR(VLOOKUP(E3, LightSkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(E3, HeavySkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(E3, UtilitySkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))))</f>
         <v>화염 강타</v>
       </c>
       <c r="G3" s="1">
-        <f>LightSKilltable!C12</f>
+        <f>LightSkilltable!C12</f>
         <v>10010</v>
       </c>
       <c r="H3" s="8" t="str">
-        <f>IF(G3="","", IFERROR(VLOOKUP(G3, LightSKilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, HeavySkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, UtilitySkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))))</f>
+        <f>IF(G3="","", IFERROR(VLOOKUP(G3, LightSkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, HeavySkilltable!$C$3:$D$1000, 2, FALSE), IFERROR(VLOOKUP(G3, UtilitySkilltable!$C$3:$D$1000, 2, FALSE), "미등록"))))</f>
         <v>플레어 탄환</v>
       </c>
     </row>
@@ -3110,7 +3130,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11F613E-218D-4C8F-A69F-11181025131C}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
@@ -3122,47 +3142,49 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="C1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
+    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="C1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F1" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>72</v>
+      <c r="C2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A100">IF(C3:C100="","", "RarityData")</f>
         <v>RarityData</v>
@@ -3172,33 +3194,37 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="E3" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="str">
+      <c r="F3" s="8"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="str">
         <v>RarityData</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="16">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>75</v>
+      <c r="C4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="E4" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" s="16"/>
+      <c r="J4" s="16"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3206,16 +3232,18 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="E5" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="16"/>
+      <c r="J5" s="16"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3223,16 +3251,18 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3240,33 +3270,37 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="E7" s="1">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="str">
+      <c r="F7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="str">
         <v>RarityData</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="16">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>79</v>
+      <c r="C8" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="E8" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3274,126 +3308,159 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="F16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="F17" s="16"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="str">
+        <v/>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="str">
+        <v/>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
         <v/>
       </c>
@@ -3793,22 +3860,22 @@
         <v>24</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J1" s="7"/>
       <c r="K1" s="5"/>
@@ -3829,25 +3896,25 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J2" s="6"/>
       <c r="P2" s="11"/>
@@ -3873,13 +3940,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="F3" s="8"/>
       <c r="J3" s="8"/>
@@ -3892,13 +3959,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -3909,13 +3976,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -3926,13 +3993,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -3943,13 +4010,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -3960,13 +4027,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -3977,13 +4044,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -3994,13 +4061,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -4011,13 +4078,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -4028,13 +4095,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -4499,10 +4566,10 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4516,7 +4583,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/SkillDatatable.xlsx
+++ b/SkillDatatable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\SBSAcademy_Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A48EF2-21A9-4457-B47C-A2E0C668B4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3861793-B7C9-4CE8-A94B-5FA0C9505A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
   <sheets>
     <sheet name="LightSkilltable" sheetId="1" r:id="rId1"/>
@@ -44,33 +44,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={6F7FBE58-685A-4AA7-A0BE-1BF48973091C}</author>
-    <author>tc={074FA935-8F2B-432E-A31A-643FCF6FAFED}</author>
-  </authors>
-  <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    상성 시스템 추가 시 필요</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="1" shapeId="0" xr:uid="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    상성 시스템 추가 시 필요</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -94,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="239">
   <si>
     <t>num</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -104,14 +77,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Icon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -124,10 +89,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cast_type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Cast_Time</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -144,10 +105,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Area_size</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Hit_Count</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -176,10 +133,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Scaling_stat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Scaling_Factor</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -197,10 +150,6 @@
   </si>
   <si>
     <t>아이콘 경로</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>소모 자원 종류</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -352,10 +301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>스킬 등급 식별자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rarity_Frame_Res</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -469,10 +414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Type_explanation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rare</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -525,10 +466,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_name_eng</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_ICE_BULLET</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -722,22 +659,6 @@
   </si>
   <si>
     <t>Element_Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Advantage_Element</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weakness_Element</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>유리한 상성 속성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>불리한 상성 속성</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -968,10 +889,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_key</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rarity_Weight</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -980,16 +897,92 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_explanation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST</t>
+    <t>속성 아이디</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>소모 자원 종류
-(HP/ST)</t>
+(HP/MP/Count)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Color_Hex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area_Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cast_Type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scaling_Stat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Explanation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Name_Eng</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type_Explanation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area_Param_Radius</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area_Param_Angle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area_Param_Width</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>너비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>길이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area_Param_Length</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1132,7 +1125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1184,6 +1177,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="40% - 강조색2" xfId="1" builtinId="35"/>
@@ -1204,9 +1200,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="donghyun koo" id="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" userId="0bec2bb6862b3cce" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1524,17 +1518,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H2" dT="2026-10-21T17:17:46.30" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{6F7FBE58-685A-4AA7-A0BE-1BF48973091C}">
-    <text>상성 시스템 추가 시 필요</text>
-  </threadedComment>
-  <threadedComment ref="I2" dT="2026-10-21T17:17:55.72" personId="{FDA12EF4-5809-48F4-912A-22B102AA65A4}" id="{074FA935-8F2B-432E-A31A-643FCF6FAFED}">
-    <text>상성 시스템 추가 시 필요</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A07B8D-296F-4731-B27A-9CC1CD5CA71B}">
   <sheetPr codeName="Sheet1"/>
@@ -1579,100 +1562,100 @@
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="K1" s="9" t="s">
+      <c r="O1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="R1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="U1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="AH1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1683,100 +1666,100 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="I2" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="L2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="AB2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="AC2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="AD2" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF2" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="AG2" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -1793,23 +1776,23 @@
         <v>10001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -1824,22 +1807,22 @@
         <v>10002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -1853,22 +1836,22 @@
         <v>10003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -1882,22 +1865,22 @@
         <v>10004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -1911,22 +1894,22 @@
         <v>10005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -1940,22 +1923,22 @@
         <v>10006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -1969,22 +1952,22 @@
         <v>10007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -1998,22 +1981,22 @@
         <v>10008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2027,22 +2010,22 @@
         <v>10009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2056,22 +2039,22 @@
         <v>10010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -2085,22 +2068,22 @@
         <v>10011</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2153,100 +2136,100 @@
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="P1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="R1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="U1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="AH1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2257,100 +2240,100 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="I2" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="AB2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="AC2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="AD2" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF2" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="AG2" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2367,19 +2350,19 @@
         <v>20001</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2394,19 +2377,19 @@
         <v>20002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2420,19 +2403,19 @@
         <v>20003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2446,19 +2429,19 @@
         <v>20004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2472,19 +2455,19 @@
         <v>20005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2537,100 +2520,100 @@
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="P1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="R1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="U1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="AH1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2641,100 +2624,100 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="I2" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="AB2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="AC2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="AD2" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF2" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="AG2" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -2751,16 +2734,19 @@
         <v>30001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2775,16 +2761,19 @@
         <v>30002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -2798,16 +2787,19 @@
         <v>30003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -2821,16 +2813,19 @@
         <v>30004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -2844,16 +2839,19 @@
         <v>30005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -2867,16 +2865,19 @@
         <v>30006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>165</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -2890,16 +2891,19 @@
         <v>30007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -2913,16 +2917,19 @@
         <v>30008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -2936,16 +2943,19 @@
         <v>30009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -2959,21 +2969,25 @@
         <v>30010</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3020,22 +3034,22 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -3055,22 +3069,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>2</v>
+        <v>229</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
@@ -3130,7 +3144,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11F613E-218D-4C8F-A69F-11181025131C}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
@@ -3142,25 +3156,24 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3168,23 +3181,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A100">IF(C3:C100="","", "RarityData")</f>
         <v>RarityData</v>
@@ -3194,37 +3206,34 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E3" s="1">
         <v>60</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="str">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="str">
         <v>RarityData</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>73</v>
+      <c r="C4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E4" s="1">
         <v>23</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3232,18 +3241,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="E5" s="1">
         <v>11</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="J5" s="16"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3251,18 +3258,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="J6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3270,37 +3275,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="E7" s="1">
         <v>1.7</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="J7" s="16"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="str">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="str">
         <v>RarityData</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>77</v>
+      <c r="C8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="E8" s="1">
         <v>0.3</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -3308,159 +3309,126 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v/>
       </c>
-      <c r="F10" s="16"/>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v/>
       </c>
-      <c r="F11" s="16"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v/>
       </c>
-      <c r="F12" s="16"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v/>
       </c>
-      <c r="F13" s="16"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v/>
       </c>
-      <c r="F14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v/>
       </c>
-      <c r="F15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v/>
       </c>
-      <c r="F16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <v/>
       </c>
-      <c r="F17" s="16"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="str">
-        <v/>
-      </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <v/>
       </c>
-      <c r="F19" s="16"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="str">
-        <v/>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
         <v/>
       </c>
@@ -3813,7 +3781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51ACD7B-A0C5-4F99-B733-4FAD1F959008}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51ACD7B-A0C5-4F99-B733-4FAD1F959008}">
   <dimension ref="A1:AG100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3823,7 +3791,7 @@
     <col min="4" max="4" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.375" style="1" bestFit="1" customWidth="1"/>
@@ -3857,27 +3825,23 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J1" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="H1" s="16"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -3896,27 +3860,20 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J2" s="6"/>
+        <v>221</v>
+      </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
@@ -3940,16 +3897,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="J3" s="8"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
@@ -3959,13 +3916,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -3976,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -3993,13 +3950,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -4010,13 +3967,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -4027,13 +3984,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -4044,13 +4001,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -4061,13 +4018,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -4078,13 +4035,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -4095,13 +4052,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -4547,32 +4504,46 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99735A9E-1F4C-49FA-B08E-163A4BA1017B}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4580,13 +4551,25 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">IF(COUNTA(C3:C1000)=0, "", _xlfn.SEQUENCE(COUNTA(C3:C1000)))</f>
         <v/>
